--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>요구사항 ID</t>
   </si>
@@ -142,259 +142,6 @@
   </si>
   <si>
     <t>기획중</t>
-  </si>
-  <si>
-    <t>REQ-F-002</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>파라미터</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>환경별</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>오버라이드</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>수집</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">	Helm values, Kustomize overlay, ApplicationSet generator </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>등을</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>통해</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>환경</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>(dev/stg/prod)</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>별로</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>분기된</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>파라미터를</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>수집</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>병합한다</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">DEV: </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>이민규</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">
-SE : </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>양형석</t>
-    </r>
-  </si>
-  <si>
-    <t>개발중</t>
   </si>
 </sst>
 </file>
@@ -809,39 +556,17 @@
       <c r="L2" s="2"/>
     </row>
     <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" ht="16.5" customHeight="1">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\sourcecode\Java-Service-Tree-Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5A79DF-CF68-453D-BAC6-7D9A61D82056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8473175A-0E81-4222-8AC9-8818C3B41C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11535" yWindow="-18645" windowWidth="32670" windowHeight="15375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45" yWindow="1275" windowWidth="25710" windowHeight="15375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="요구사항정의서" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">[개요]
+    <t>[개요]
 현재 A-RMS 기능 페이지는 단순 기능의 설명과 이미지로만 표시되어 사용자에게 내용을 전달하기가 어렵다.
 따라서, 각 라이선스 타입에 따라 ( POC, PRO, ENT ) 실제 액션의 흐름을 표시하여,
 A-RMS의 기능을 전달하고자 한다.
@@ -244,11 +244,13 @@
 - N/A
 [검증 기준]
 - common.css 와 기존에 구현된 html에서 사용된 css를 전부 확인하여, 통일성있는 디자인과 색감을 사용할 것.
+[작업 대상]
+Java-Service-Tree-Framework-Frontend-Web 모듈의 arms\html\landing_function에 작업해 줘
+기존 작업은 무시하고 작업 해
 [Worker Settings]
 - MainWoker : claude-main
 - SubWorker : ollama
-- MainWoker-SubAgent : frontend-expert
-</t>
+- MainWoker-SubAgent : frontend-expert</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\sourcecode\Java-Service-Tree-Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8473175A-0E81-4222-8AC9-8818C3B41C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EE37CB-0C32-4115-AF32-DECCB2CD9D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="1275" windowWidth="25710" windowHeight="15375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="555" yWindow="1650" windowWidth="21990" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="요구사항정의서" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
   <si>
     <t>요구사항 ID</t>
   </si>
@@ -225,6 +225,47 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
+    <t>DEV</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발팀 이동민</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀티에이전트를 지원하기 위하여, 개발용 에이전트먀 ( Role : Reviewer ) 를 구성하기</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>REQ-AIAGENT-DEV-02</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>[개요]
+멀티에이전트 워커 풀에서 ollama 워커를 완전 삭제하고,
+그 자리를 결정론적 검사 + RAG 기반 LLM 판정의 하이브리드 Reviewer Agent 를 구성하려고 한다.
+설계 방향:
+Spring AI 프레임워크를 기반으로
+멀티 에이전트로써 Reviewer Agent 기능을 탑재한다.
+Opensearch 의 벡터 디비를 활용해서, 리뷰를 진행할 수 있는 기능도 추가한다.
+[상세 기능 요구사항]
+PMBOK 을 기준으로 Project Charter 와 SRS 를 작성한다.
+[입력 / 출력]
+[제약 조건 / 비기능 요구사항]
+[검증 기준]
+[작업 대상]
+Dev-Ai-Agent 프로젝트
+[Worker Settings]
+- MainWorker                : claude-main
+- SubWorker                 : codex-critic
+- MainWorker-SubAgent   : N/A</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>[개요]
 현재 A-RMS 기능 페이지는 단순 기능의 설명과 이미지로만 표시되어 사용자에게 내용을 전달하기가 어렵다.
 따라서, 각 라이선스 타입에 따라 ( POC, PRO, ENT ) 실제 액션의 흐름을 표시하여,
@@ -237,6 +278,18 @@
 5) 선정된 이슈를 자동으로 A-RMS 가 수집한다.
 6) 수집된 데이터를 기반으로 Time, Scope, Resource, Cost 관점으로 분석된 결과를 확인한다.
 7) 개인의 성과지표를 확인하고, 주간 보고 리포트를 생성하여 확인 할 수 있다.
+1) PRO 타입에 대해서, 화면을 구성하되, 맨 처음. 고객의 JIRA 와 A-RMS 를 연결한다.
+2) 연결 후 Default 프로젝트의 Base Version 으로 고객사의 JIRA 프로젝트를 설정한다.
+3) 설정 후 . 자동으로 Mapping 된 이슈의 타입 별. 우선순위와 유형을 확인한다.
+4) 2) 연결 후. PM이나 팀장은 요구사항 정의서, 혹은 간트차트 ( XLGannt ), 또는 웹UI에서 요구사항을 구성한다.
+5) 구성된 요구사항은 자동으로 JIRA 이슈로 배포된다. ( 특허 )
+6) 배포된 요구사항 이슈를 기반으로 실무자는 작업을 진행한다 ( 하위이슈, 연결이슈 )
+7) A-RMS 는 배포된 요구사항 이슈를 기반으로 연결된, 하위의 이슈를 모두 수집한다.
+8) 수집된 결과를 현황 관리에서 목록과 달력 UI기반으로 확인할 수 있다.
+8) 또한, 수집된 데이터를 기반으로 Time, Scope, Resource, Cost 관점으로 분석된 결과를 확인한다.
+9) 프로젝트의 성과지표를 확인하고, SWOT 차트로 요구사항의 우선순위를 조정할 수 있는 기능을 제공한다.
+10) 개인의 성과지표를 확인하고, 주간 보고 리포트를 생성하여 확인 할 수 있다.
+11) 요구사항별로 성과지표를 확인 할 수 있다.
 [입력 / 출력]
 - 입력: 고객사의 JIRA 접속 정보 ( Admin 권한 필요 )
 - 출력: Time, Scope, Resource, Cost 관점의 리포트, 개인 KPI 지표, 주간 보고 리포트
@@ -249,7 +302,7 @@
 기존 작업은 무시하고 작업 해
 [Worker Settings]
 - MainWoker : claude-main
-- SubWorker : ollama
+- SubWorker : codex-critic
 - MainWoker-SubAgent : frontend-expert</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -341,7 +394,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,6 +404,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -396,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -429,6 +488,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -869,7 +934,7 @@
         <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -890,19 +955,41 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
+    <row r="3" spans="1:12" ht="337.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -8182,39 +8269,39 @@
       </c>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
     </row>
     <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
     </row>
     <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
     </row>
     <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\sourcecode\Java-Service-Tree-Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EE37CB-0C32-4115-AF32-DECCB2CD9D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61999FE-C418-46ED-81A8-E08CEAAC2FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="1650" windowWidth="21990" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9795" yWindow="-21600" windowWidth="28950" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="요구사항정의서" sheetId="1" r:id="rId1"/>
@@ -278,6 +278,7 @@
 5) 선정된 이슈를 자동으로 A-RMS 가 수집한다.
 6) 수집된 데이터를 기반으로 Time, Scope, Resource, Cost 관점으로 분석된 결과를 확인한다.
 7) 개인의 성과지표를 확인하고, 주간 보고 리포트를 생성하여 확인 할 수 있다.
+---
 1) PRO 타입에 대해서, 화면을 구성하되, 맨 처음. 고객의 JIRA 와 A-RMS 를 연결한다.
 2) 연결 후 Default 프로젝트의 Base Version 으로 고객사의 JIRA 프로젝트를 설정한다.
 3) 설정 후 . 자동으로 Mapping 된 이슈의 타입 별. 우선순위와 유형을 확인한다.
@@ -290,11 +291,35 @@
 9) 프로젝트의 성과지표를 확인하고, SWOT 차트로 요구사항의 우선순위를 조정할 수 있는 기능을 제공한다.
 10) 개인의 성과지표를 확인하고, 주간 보고 리포트를 생성하여 확인 할 수 있다.
 11) 요구사항별로 성과지표를 확인 할 수 있다.
+---
+1) ENT 타입에 대해서, 화면을 구성하되, 맨 처음. 고객의 JIRA 와 A-RMS 를 연결한다.
+2) 연결 후 Default 프로젝트의 Base Version 으로 고객사의 JIRA 프로젝트를 설정한다.
+3) 설정 후 . 자동으로 Mapping 된 이슈의 타입 별. 우선순위와 유형을 확인한다.
+4) 각종 산출물을 A-RMS 에 업로드하거나, ( word, excel, pdf 등등 ) , Wiki 문서를 작성한다.
+5) 업로드된 파일을 파싱하고, Wiki 문서의 일부를 드래그하여, A-RMS 의 요구사항으로 등록한다.
+6) 또는 문서의 요구사항을 파싱하여, Ai를 활용하여 자동으로 요구사항 항목을 추천하여, 등록한다.
+7) 또는 PM이나 팀장은 요구사항 정의서, 혹은 간트차트 ( XLGannt ), 또는 웹UI에서 요구사항을 등록한다.
+8) 등록된 요구사항은 자동으로 JIRA 이슈로 배포된다. ( 특허 )
+9) 배포된 요구사항 이슈를 기반으로 실무자는 작업을 진행한다 ( 하위이슈, 연결이슈 )
+7) A-RMS 는 배포된 요구사항 이슈를 기반으로 연결된, 하위의 이슈를 모두 수집한다.
+8) 수집된 결과를 현황 관리에서 목록과 달력 UI기반으로 확인할 수 있다.
+8) 또한, 수집된 데이터를 기반으로 Time, Scope, Resource, Cost 관점으로 분석된 결과를 확인한다.
+9) 프로젝트의 성과지표를 확인하고, SWOT 차트로 요구사항의 우선순위를 조정할 수 있는 기능을 제공한다.
+10) 개인의 성과지표를 확인하고, 주간 보고 리포트를 생성하여 확인 할 수 있다.
+11) 요구사항별로 성과지표를 확인 할 수 있다.
+---
+1) 이와는 별개로, 각 사용자별로 개별적인 Dashboard 를 제공하고 개인의 지표를 확인 할 수 있으며
+2) 실무자별로 할당된 프로젝트와 산출물을 조회하고, 
+3) 프로젝트의 버전별 목표를 조회할 수 있고
+4) 권한을 가진 Wiki 와 산출물을 조회할 수 있으며
+5) 요구사항의 상세한 내용과 질의를 연계하여 제공할 수 있습니다.
 [입력 / 출력]
-- 입력: 고객사의 JIRA 접속 정보 ( Admin 권한 필요 )
-- 출력: Time, Scope, Resource, Cost 관점의 리포트, 개인 KPI 지표, 주간 보고 리포트
+- N/A
 [제약 조건 / 비기능 요구사항]
-- N/A
+- 본 퍼블리싱은 최대한 사용자 관점에서 A-RMS를 사용함에 있어 라이선스 타입별로
+  사용자의 시나리오 흐름으로 표시되어야 한다. ( 최대한 일러스트 아이콘을 활용할 것 )
+  실제 업무 흐름을 한줄로 표시하고, 한줄 표시를 SVG 로 구현하되 일러스트 아이콘을 활용하며
+  각 단계는 축약된 단어로 구성하고, 아래 페이지 영역에서 해당 단계를 설명하는 구조로 퍼블리싱 해줘
 [검증 기준]
 - common.css 와 기존에 구현된 html에서 사용된 css를 전부 확인하여, 통일성있는 디자인과 색감을 사용할 것.
 [작업 대상]
